--- a/log.xlsx
+++ b/log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2667,172 +2667,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B54" t="n">
-        <v>0</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>DC-2</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>J-3700</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>22</v>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="n">
-        <v>1400</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>57.84317</v>
-      </c>
-      <c r="J54" t="n">
-        <v>2.50048</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0.17683</v>
-      </c>
-      <c r="L54" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>53</v>
-      </c>
-      <c r="B55" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>J-3700</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>J-3701</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>21</v>
-      </c>
-      <c r="F55" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G55" t="n">
-        <v>1300</v>
-      </c>
-      <c r="H55" t="n">
-        <v>57.84317</v>
-      </c>
-      <c r="I55" t="n">
-        <v>57.17014</v>
-      </c>
-      <c r="J55" t="n">
-        <v>2.18578</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0.7130300000000001</v>
-      </c>
-      <c r="L55" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>54</v>
-      </c>
-      <c r="B56" t="n">
-        <v>2</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>J-3701</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>J-3702</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>20</v>
-      </c>
-      <c r="F56" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G56" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H56" t="n">
-        <v>57.84317</v>
-      </c>
-      <c r="I56" t="n">
-        <v>65.79558</v>
-      </c>
-      <c r="J56" t="n">
-        <v>2.55961</v>
-      </c>
-      <c r="K56" t="n">
-        <v>4.27759</v>
-      </c>
-      <c r="L56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>55</v>
-      </c>
-      <c r="B57" t="n">
-        <v>3</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>J-3702</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>J-3703</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>20</v>
-      </c>
-      <c r="F57" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G57" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H57" t="n">
-        <v>57.84317</v>
-      </c>
-      <c r="I57" t="n">
-        <v>59.47049</v>
-      </c>
-      <c r="J57" t="n">
-        <v>2.12105</v>
-      </c>
-      <c r="K57" t="n">
-        <v>1.00268</v>
-      </c>
-      <c r="L57" t="b">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
